--- a/서버정보/20260521_리소스배포_테스트_임시_FE2생성.xlsx
+++ b/서버정보/20260521_리소스배포_테스트_임시_FE2생성.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011C272D-4741-4C0F-8E9B-6DBFC209BDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E04155-3A8E-4006-A598-BEB5F79C4660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4846" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4807" uniqueCount="629">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -29154,8 +29154,9 @@
       <c r="B4" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="74" t="s">
-        <v>182</v>
+      <c r="C4" s="74" t="str" cm="1">
+        <f t="array" ref="C4">UPPER(INDEX(_xlfn.TEXTSPLIT($F4, "-"), 3))</f>
+        <v>BDP</v>
       </c>
       <c r="D4" s="74" t="s">
         <v>386</v>
@@ -29207,8 +29208,9 @@
       <c r="B5" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="84" t="s">
-        <v>182</v>
+      <c r="C5" s="84" t="str" cm="1">
+        <f t="array" ref="C5">UPPER(INDEX(_xlfn.TEXTSPLIT($F5, "-"), 3))</f>
+        <v>BDP</v>
       </c>
       <c r="D5" s="84" t="s">
         <v>386</v>
@@ -29311,8 +29313,9 @@
       <c r="B7" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="84" t="s">
-        <v>182</v>
+      <c r="C7" s="84" t="str" cm="1">
+        <f t="array" ref="C7">UPPER(INDEX(_xlfn.TEXTSPLIT($F7, "-"), 3))</f>
+        <v>CS</v>
       </c>
       <c r="D7" s="84" t="s">
         <v>205</v>
@@ -29364,8 +29367,9 @@
       <c r="B8" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C8" s="74" t="s">
-        <v>182</v>
+      <c r="C8" s="74" t="str" cm="1">
+        <f t="array" ref="C8">UPPER(INDEX(_xlfn.TEXTSPLIT($F8, "-"), 3))</f>
+        <v>CS</v>
       </c>
       <c r="D8" s="74" t="s">
         <v>205</v>
@@ -29417,8 +29421,9 @@
       <c r="B9" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C9" s="84" t="s">
-        <v>182</v>
+      <c r="C9" s="84" t="str" cm="1">
+        <f t="array" ref="C9">UPPER(INDEX(_xlfn.TEXTSPLIT($F9, "-"), 3))</f>
+        <v>CS</v>
       </c>
       <c r="D9" s="84" t="s">
         <v>205</v>
@@ -29470,8 +29475,9 @@
       <c r="B10" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C10" s="84" t="s">
-        <v>182</v>
+      <c r="C10" s="84" t="str" cm="1">
+        <f t="array" ref="C10">UPPER(INDEX(_xlfn.TEXTSPLIT($F10, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="D10" s="84" t="s">
         <v>286</v>
@@ -29523,8 +29529,9 @@
       <c r="B11" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C11" s="74" t="s">
-        <v>182</v>
+      <c r="C11" s="74" t="str" cm="1">
+        <f t="array" ref="C11">UPPER(INDEX(_xlfn.TEXTSPLIT($F11, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="D11" s="74" t="s">
         <v>286</v>
@@ -29576,8 +29583,9 @@
       <c r="B12" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C12" s="84" t="s">
-        <v>182</v>
+      <c r="C12" s="84" t="str" cm="1">
+        <f t="array" ref="C12">UPPER(INDEX(_xlfn.TEXTSPLIT($F12, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="D12" s="84" t="s">
         <v>286</v>
@@ -29629,8 +29637,9 @@
       <c r="B13" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C13" s="74" t="s">
-        <v>182</v>
+      <c r="C13" s="74" t="str" cm="1">
+        <f t="array" ref="C13">UPPER(INDEX(_xlfn.TEXTSPLIT($F13, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="D13" s="74" t="s">
         <v>286</v>
@@ -29682,8 +29691,9 @@
       <c r="B14" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="84" t="s">
-        <v>182</v>
+      <c r="C14" s="84" t="str" cm="1">
+        <f t="array" ref="C14">UPPER(INDEX(_xlfn.TEXTSPLIT($F14, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="D14" s="84" t="s">
         <v>286</v>
@@ -29735,8 +29745,9 @@
       <c r="B15" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C15" s="74" t="s">
-        <v>182</v>
+      <c r="C15" s="74" t="str" cm="1">
+        <f t="array" ref="C15">UPPER(INDEX(_xlfn.TEXTSPLIT($F15, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="D15" s="74" t="s">
         <v>286</v>
@@ -29788,8 +29799,9 @@
       <c r="B16" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C16" s="84" t="s">
-        <v>182</v>
+      <c r="C16" s="84" t="str" cm="1">
+        <f t="array" ref="C16">UPPER(INDEX(_xlfn.TEXTSPLIT($F16, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="D16" s="84" t="s">
         <v>286</v>
@@ -29841,8 +29853,9 @@
       <c r="B17" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C17" s="74" t="s">
-        <v>182</v>
+      <c r="C17" s="74" t="str" cm="1">
+        <f t="array" ref="C17">UPPER(INDEX(_xlfn.TEXTSPLIT($F17, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="D17" s="74" t="s">
         <v>286</v>
@@ -29894,8 +29907,9 @@
       <c r="B18" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C18" s="84" t="s">
-        <v>182</v>
+      <c r="C18" s="84" t="str" cm="1">
+        <f t="array" ref="C18">UPPER(INDEX(_xlfn.TEXTSPLIT($F18, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="D18" s="84" t="s">
         <v>286</v>
@@ -29947,8 +29961,9 @@
       <c r="B19" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C19" s="74" t="s">
-        <v>182</v>
+      <c r="C19" s="74" t="str" cm="1">
+        <f t="array" ref="C19">UPPER(INDEX(_xlfn.TEXTSPLIT($F19, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="D19" s="74" t="s">
         <v>286</v>
@@ -30000,8 +30015,9 @@
       <c r="B20" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C20" s="84" t="s">
-        <v>182</v>
+      <c r="C20" s="84" t="str" cm="1">
+        <f t="array" ref="C20">UPPER(INDEX(_xlfn.TEXTSPLIT($F20, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="D20" s="84" t="s">
         <v>286</v>
@@ -30053,8 +30069,9 @@
       <c r="B21" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C21" s="74" t="s">
-        <v>182</v>
+      <c r="C21" s="74" t="str" cm="1">
+        <f t="array" ref="C21">UPPER(INDEX(_xlfn.TEXTSPLIT($F21, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="D21" s="74" t="s">
         <v>286</v>
@@ -30106,8 +30123,9 @@
       <c r="B22" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C22" s="84" t="s">
-        <v>182</v>
+      <c r="C22" s="84" t="str" cm="1">
+        <f t="array" ref="C22">UPPER(INDEX(_xlfn.TEXTSPLIT($F22, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="D22" s="84" t="s">
         <v>286</v>
@@ -30159,8 +30177,9 @@
       <c r="B23" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C23" s="74" t="s">
-        <v>182</v>
+      <c r="C23" s="74" t="str" cm="1">
+        <f t="array" ref="C23">UPPER(INDEX(_xlfn.TEXTSPLIT($F23, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="D23" s="74" t="s">
         <v>286</v>
@@ -30212,8 +30231,9 @@
       <c r="B24" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C24" s="74" t="s">
-        <v>182</v>
+      <c r="C24" s="74" t="str" cm="1">
+        <f t="array" ref="C24">UPPER(INDEX(_xlfn.TEXTSPLIT($F24, "-"), 3))</f>
+        <v>DOIP</v>
       </c>
       <c r="D24" s="74" t="s">
         <v>388</v>
@@ -30265,8 +30285,9 @@
       <c r="B25" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C25" s="84" t="s">
-        <v>182</v>
+      <c r="C25" s="84" t="str" cm="1">
+        <f t="array" ref="C25">UPPER(INDEX(_xlfn.TEXTSPLIT($F25, "-"), 3))</f>
+        <v>DOIP</v>
       </c>
       <c r="D25" s="84" t="s">
         <v>388</v>
@@ -30318,8 +30339,9 @@
       <c r="B26" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C26" s="74" t="s">
-        <v>182</v>
+      <c r="C26" s="74" t="str" cm="1">
+        <f t="array" ref="C26">UPPER(INDEX(_xlfn.TEXTSPLIT($F26, "-"), 3))</f>
+        <v>DOIP</v>
       </c>
       <c r="D26" s="74" t="s">
         <v>388</v>
@@ -30371,8 +30393,9 @@
       <c r="B27" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C27" s="74" t="s">
-        <v>182</v>
+      <c r="C27" s="74" t="str" cm="1">
+        <f t="array" ref="C27">UPPER(INDEX(_xlfn.TEXTSPLIT($F27, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D27" s="74" t="s">
         <v>385</v>
@@ -30424,8 +30447,9 @@
       <c r="B28" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C28" s="84" t="s">
-        <v>182</v>
+      <c r="C28" s="84" t="str" cm="1">
+        <f t="array" ref="C28">UPPER(INDEX(_xlfn.TEXTSPLIT($F28, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D28" s="84" t="s">
         <v>385</v>
@@ -30477,8 +30501,9 @@
       <c r="B29" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C29" s="74" t="s">
-        <v>182</v>
+      <c r="C29" s="74" t="str" cm="1">
+        <f t="array" ref="C29">UPPER(INDEX(_xlfn.TEXTSPLIT($F29, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D29" s="74" t="s">
         <v>385</v>
@@ -30530,8 +30555,9 @@
       <c r="B30" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C30" s="84" t="s">
-        <v>182</v>
+      <c r="C30" s="84" t="str" cm="1">
+        <f t="array" ref="C30">UPPER(INDEX(_xlfn.TEXTSPLIT($F30, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D30" s="84" t="s">
         <v>385</v>
@@ -30583,8 +30609,9 @@
       <c r="B31" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C31" s="74" t="s">
-        <v>182</v>
+      <c r="C31" s="74" t="str" cm="1">
+        <f t="array" ref="C31">UPPER(INDEX(_xlfn.TEXTSPLIT($F31, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D31" s="74" t="s">
         <v>385</v>
@@ -30636,8 +30663,9 @@
       <c r="B32" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C32" s="84" t="s">
-        <v>182</v>
+      <c r="C32" s="84" t="str" cm="1">
+        <f t="array" ref="C32">UPPER(INDEX(_xlfn.TEXTSPLIT($F32, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D32" s="84" t="s">
         <v>385</v>
@@ -30689,8 +30717,9 @@
       <c r="B33" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C33" s="74" t="s">
-        <v>182</v>
+      <c r="C33" s="74" t="str" cm="1">
+        <f t="array" ref="C33">UPPER(INDEX(_xlfn.TEXTSPLIT($F33, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D33" s="74" t="s">
         <v>385</v>
@@ -30742,8 +30771,9 @@
       <c r="B34" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C34" s="84" t="s">
-        <v>182</v>
+      <c r="C34" s="84" t="str" cm="1">
+        <f t="array" ref="C34">UPPER(INDEX(_xlfn.TEXTSPLIT($F34, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D34" s="84" t="s">
         <v>385</v>
@@ -30795,8 +30825,9 @@
       <c r="B35" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C35" s="74" t="s">
-        <v>182</v>
+      <c r="C35" s="74" t="str" cm="1">
+        <f t="array" ref="C35">UPPER(INDEX(_xlfn.TEXTSPLIT($F35, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D35" s="74" t="s">
         <v>385</v>
@@ -30848,8 +30879,9 @@
       <c r="B36" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C36" s="84" t="s">
-        <v>182</v>
+      <c r="C36" s="84" t="str" cm="1">
+        <f t="array" ref="C36">UPPER(INDEX(_xlfn.TEXTSPLIT($F36, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D36" s="84" t="s">
         <v>385</v>
@@ -30901,8 +30933,9 @@
       <c r="B37" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C37" s="74" t="s">
-        <v>182</v>
+      <c r="C37" s="74" t="str" cm="1">
+        <f t="array" ref="C37">UPPER(INDEX(_xlfn.TEXTSPLIT($F37, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D37" s="74" t="s">
         <v>385</v>
@@ -30954,8 +30987,9 @@
       <c r="B38" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C38" s="84" t="s">
-        <v>182</v>
+      <c r="C38" s="84" t="str" cm="1">
+        <f t="array" ref="C38">UPPER(INDEX(_xlfn.TEXTSPLIT($F38, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D38" s="84" t="s">
         <v>385</v>
@@ -31007,8 +31041,9 @@
       <c r="B39" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C39" s="74" t="s">
-        <v>182</v>
+      <c r="C39" s="74" t="str" cm="1">
+        <f t="array" ref="C39">UPPER(INDEX(_xlfn.TEXTSPLIT($F39, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D39" s="74" t="s">
         <v>385</v>
@@ -31060,8 +31095,9 @@
       <c r="B40" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C40" s="84" t="s">
-        <v>182</v>
+      <c r="C40" s="84" t="str" cm="1">
+        <f t="array" ref="C40">UPPER(INDEX(_xlfn.TEXTSPLIT($F40, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D40" s="84" t="s">
         <v>385</v>
@@ -31113,8 +31149,9 @@
       <c r="B41" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="74" t="s">
-        <v>182</v>
+      <c r="C41" s="74" t="str" cm="1">
+        <f t="array" ref="C41">UPPER(INDEX(_xlfn.TEXTSPLIT($F41, "-"), 3))</f>
+        <v>DTG</v>
       </c>
       <c r="D41" s="74" t="s">
         <v>385</v>
@@ -31166,8 +31203,9 @@
       <c r="B42" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C42" s="84" t="s">
-        <v>182</v>
+      <c r="C42" s="84" t="str" cm="1">
+        <f t="array" ref="C42">UPPER(INDEX(_xlfn.TEXTSPLIT($F42, "-"), 3))</f>
+        <v>IF</v>
       </c>
       <c r="D42" s="84" t="s">
         <v>480</v>
@@ -31219,8 +31257,9 @@
       <c r="B43" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C43" s="74" t="s">
-        <v>182</v>
+      <c r="C43" s="74" t="str" cm="1">
+        <f t="array" ref="C43">UPPER(INDEX(_xlfn.TEXTSPLIT($F43, "-"), 3))</f>
+        <v>IF</v>
       </c>
       <c r="D43" s="74" t="s">
         <v>480</v>
@@ -34156,21 +34195,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -34314,10 +34338,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34339,19 +34388,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>